--- a/artfynd/S 654-2025 artfynd.xlsx
+++ b/artfynd/S 654-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AZ89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531379</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531381</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531401</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531403</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538103</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1384,6 +1414,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/214434</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1505,6 +1540,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531357</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1626,6 +1666,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531365</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1747,6 +1792,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531367</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1868,6 +1918,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531369</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1989,6 +2044,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531372</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2110,6 +2170,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531376</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2231,6 +2296,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531377</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2352,6 +2422,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531380</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2473,6 +2548,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531382</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2594,6 +2674,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531384</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2715,6 +2800,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531385</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2836,6 +2926,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531391</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2957,6 +3052,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531393</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3078,6 +3178,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531395</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3199,6 +3304,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531397</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3320,6 +3430,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531399</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3441,6 +3556,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531402</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3562,6 +3682,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531404</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3683,6 +3808,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531406</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3804,6 +3934,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531409</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3911,6 +4046,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/344368</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4032,6 +4172,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531363</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4153,6 +4298,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531368</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4274,6 +4424,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531370</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4395,6 +4550,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531374</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4516,6 +4676,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531378</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4637,6 +4802,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531383</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4758,6 +4928,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531386</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4879,6 +5054,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531389</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5000,6 +5180,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531396</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5121,6 +5306,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531398</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5242,6 +5432,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531400</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5363,6 +5558,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531405</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5460,6 +5660,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60377427</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5582,6 +5787,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124983175</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5689,6 +5899,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1572352</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5810,6 +6025,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538092</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5931,6 +6151,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538093</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6052,6 +6277,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538094</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6173,6 +6403,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538095</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6294,6 +6529,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538096</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6415,6 +6655,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538097</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6536,6 +6781,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538100</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6657,6 +6907,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538102</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6778,6 +7033,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538104</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6899,6 +7159,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538107</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7020,6 +7285,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538110</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7141,6 +7411,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538111</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7262,6 +7537,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538112</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7383,6 +7663,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538113</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7504,6 +7789,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538114</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7625,6 +7915,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538115</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7746,6 +8041,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69525436</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7867,6 +8167,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531359</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7988,6 +8293,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531373</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8109,6 +8419,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531375</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8230,6 +8545,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531387</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8351,6 +8671,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531390</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8472,6 +8797,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531392</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8593,6 +8923,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531394</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8714,6 +9049,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69531408</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8827,6 +9167,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124983810</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8946,6 +9291,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115712100</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9065,6 +9415,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115712099</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9184,6 +9539,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115712096</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9305,6 +9665,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69514484</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9426,6 +9791,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69514485</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9547,6 +9917,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90670552</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9658,6 +10033,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60377418</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9774,6 +10154,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60377419</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9886,6 +10271,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124983607</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10037,6 +10427,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714222</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10188,6 +10583,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714232</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10339,6 +10739,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714245</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10490,6 +10895,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714276</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10641,6 +11051,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714278</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10792,6 +11207,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714279</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10911,6 +11331,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102885189</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11030,6 +11455,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115712103</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11171,6 +11601,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79719580</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11290,6 +11725,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101936087</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11396,8 +11836,103 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124983246</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>